--- a/Images/2/100StatisticalSeries.xlsx
+++ b/Images/2/100StatisticalSeries.xlsx
@@ -406,25 +406,25 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C2">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -435,25 +435,25 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="B3">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="C3">
-        <v>0.39</v>
+        <v>0.24</v>
       </c>
       <c r="D3">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="E3">
-        <v>0.09999999999999998</v>
+        <v>0.1599999999999999</v>
       </c>
       <c r="F3">
-        <v>0.06000000000000005</v>
+        <v>0.05000000000000004</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="H3">
         <v>0</v>

--- a/Images/2/100StatisticalSeries.xlsx
+++ b/Images/2/100StatisticalSeries.xlsx
@@ -409,25 +409,25 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C2">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
         <v>1</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -438,25 +438,25 @@
         <v>0.05</v>
       </c>
       <c r="B3">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="C3">
-        <v>0.24</v>
+        <v>0.33</v>
       </c>
       <c r="D3">
-        <v>0.28</v>
+        <v>0.2999999999999999</v>
       </c>
       <c r="E3">
-        <v>0.1599999999999999</v>
+        <v>0.14</v>
       </c>
       <c r="F3">
-        <v>0.05000000000000004</v>
+        <v>0.02000000000000002</v>
       </c>
       <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
         <v>0.01000000000000001</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
       </c>
       <c r="I3">
         <v>0</v>

--- a/Images/2/100StatisticalSeries.xlsx
+++ b/Images/2/100StatisticalSeries.xlsx
@@ -47,6 +47,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -64,7 +67,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -72,12 +75,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -406,59 +425,59 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C2">
         <v>33</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
         <v>0</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3">
-        <v>0.05</v>
-      </c>
-      <c r="B3">
-        <v>0.15</v>
-      </c>
-      <c r="C3">
+      <c r="A3" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="C3" s="1">
         <v>0.33</v>
       </c>
-      <c r="D3">
-        <v>0.2999999999999999</v>
-      </c>
-      <c r="E3">
-        <v>0.14</v>
-      </c>
-      <c r="F3">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="G3">
+      <c r="D3" s="1">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.1599999999999999</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.04000000000000004</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="H3" s="1">
         <v>0</v>
       </c>
-      <c r="H3">
-        <v>0.01000000000000001</v>
-      </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>0</v>
       </c>
     </row>
